--- a/04-transaction-services-dd/Financial_DD_Analysis.xlsx
+++ b/04-transaction-services-dd/Financial_DD_Analysis.xlsx
@@ -18,7 +18,7 @@
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$E$12</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$F$23</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'EBIT to Net Income Bridge'!$A$1:$G$33</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Quality of Earnings'!$A$1:$F$34</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Quality of Earnings'!$A$1:$F$47</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Risk Flags'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,8 +30,78 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">FY2023A et FY2024A : D&amp;A estimée à 3,4 % du chiffre d'affaires (hypothèse personnelle, aucune ventilation D&amp;A publiée à ce niveau de détail). FY2025A : valeur réelle publiée (464 M€), identique à celle utilisée dans Three_Statement_Model.xlsx du même portfolio, pour rester cohérent entre les deux fichiers.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cohérence avec le modèle 3 états du portfolio (Three_Statement_Model.xlsx) : source présentation des résultats annuels FY2025, fnacdarty.com, 25/02/2026.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Réel : dotation aux amortissements FY2025A telle que publiée dans la présentation des résultats annuels FY2025 (fnacdarty.com, 25/02/2026), incluant l'amortissement des droits d'usage IFRS16. Même donnée que celle utilisée dans Three_Statement_Model (onglet Income Statement, cellule E8).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Réel : 123 M€ (goodwill, marque, IT, activités poursuivies) + 60 M€ (Nature &amp; Découvertes, activité cédée), communiqué de résultats annuels FY2025 (fnacdarty.com, 25/02/2026). Détail du pont en onglet EBIT to Net Income Bridge.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Réel, présentation des résultats annuels FY2025 (fnacdarty.com, 25/02/2026), périmètre Unieuro en année pleine. Même source que Three_Statement_Model, onglet Assumptions, cellule C44.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
   <si>
     <t xml:space="preserve">Financial Due Diligence (Quality of Earnings) - cas d'école sur Fnac Darty</t>
   </si>
@@ -102,7 +172,7 @@
     <t xml:space="preserve">Résultat opérationnel courant / EBIT (réel)</t>
   </si>
   <si>
-    <t xml:space="preserve">D&amp;A estimée (3,4 % du CA - hypothèse personnelle, non publiée séparément)</t>
+    <t xml:space="preserve">D&amp;A (FY2023A-FY2024A : hypothèse 3,4 % du CA ; FY2025A : réel)</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA courant estimé</t>
@@ -114,7 +184,28 @@
     <t xml:space="preserve">Marge d'EBIT courant (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : l'EBIT courant progresse chaque année (171 -&gt; 189 -&gt; 203 M€) alors que le résultat net publié chute fortement en FY2025 (-146 M€, onglet suivant) - signe que le résultat opérationnel courant est déjà "propre" (il exclut par construction les éléments non courants en normes françaises) et que la dégradation du résultat net vient d'éléments situés sous la ligne opérationnelle courante, pas d'une dégradation de l'exploitation elle-même. La légère baisse de la marge d'EBITDA en FY2025 (dilution liée à l'intégration d'Unieuro, qui opère à des marges plus faibles) mérite néanmoins d'être creusée par segment en data room.</t>
+    <t xml:space="preserve">Lecture : l'EBIT courant progresse chaque année (171 -&gt; 189 -&gt; 203 M€) alors que le résultat net publié chute fortement en FY2025 (-146 M€, onglet suivant) : signe que le résultat opérationnel courant est déjà « propre » (il exclut par construction les éléments non courants en normes françaises) et que la dégradation du résultat net vient d'éléments situés sous la ligne opérationnelle courante, pas d'une dégradation de l'exploitation elle-même. La marge d'EBITDA courant estimée progresse également sur les 3 exercices (5,6 % -&gt; 5,7 % -&gt; 6,5 %) : la dotation aux amortissements FY2025A retenue ici est la valeur réelle publiée (464 M€), ce qui fait recouper exactement l'EBITDA courant estimé (667 M€) avec l'EBITDA réel publié par la société pour cet exercice (voir section ci-dessous). Cette progression de marge mérite néanmoins d'être creusée par segment en data room compte tenu de l'intégration d'Unieuro en année pleine (voir Risk Flags).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMALISATION DE L'EBITDA : ÉLÉMENTS NON RÉCURRENTS ET RÉFÉRENCE EXTERNE (FY2025A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dépréciations non récurrentes publiées (goodwill/marque/IT + Nature &amp; Découvertes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces dépréciations sont présentées sous la ligne du résultat opérationnel courant en normes françaises : elles n'affectent ni l'EBIT courant (ligne 7) ni l'EBITDA courant estimé (ligne 9) ci-dessus, qui excluent déjà ces éléments non récurrents par construction de la présentation comptable. Aucun retraitement supplémentaire n'est donc nécessaire sur ces deux lignes pour ces éléments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autres catégories de non-récurrents usuelles (restructuration, créances douteuses, litiges, sinistres, changement de méthode comptable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non identifiées dans les communiqués publics de Fnac Darty consultés pour cet exercice. Si de tels éléments existent, ils seraient déjà inclus dans le résultat opérationnel courant sans être isolés séparément : un point à vérifier en data room plutôt qu'à supposer absent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA réel publié FY2025A (référence externe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écart EBITDA courant estimé FY2025A vs EBITDA réel publié (doit être nul)</t>
   </si>
   <si>
     <t xml:space="preserve">Pont FY2025 : résultat opérationnel courant -&gt; résultat net publié</t>
@@ -135,7 +226,7 @@
     <t xml:space="preserve">- Résultat financier, IS et autres éléments non détaillés publiquement</t>
   </si>
   <si>
-    <t xml:space="preserve">Plug non documenté publiquement (résultat financier net, IS, intérêts minoritaires) - à demander en data room plutôt qu'à estimer arbitrairement.</t>
+    <t xml:space="preserve">Plug non documenté publiquement (résultat financier net, IS, intérêts minoritaires), à demander en data room plutôt qu'à estimer arbitrairement.</t>
   </si>
   <si>
     <t xml:space="preserve">-&gt; Résultat net publié FY2025 (réel, GAAP)</t>
@@ -162,10 +253,10 @@
     <t xml:space="preserve">183 M€ de dépréciations (goodwill/marque/IT + Nature &amp; Découvertes) en une seule année. Bon signal : l'EBIT courant n'est pas affecté. Point à creuser : la valeur résiduelle du goodwill Unieuro (acquis en nov. 2024) après cette vague de dépréciations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marge d'EBITDA en légère baisse malgré la hausse du CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La consolidation d'Unieuro (retail électronique en Italie, marges historiquement plus faibles que le cœur Fnac Darty) dilue la marge groupe. A documenter par segment géographique.</t>
+    <t xml:space="preserve">Marge d'EBITDA courant en hausse sur les 3 exercices, y compris lors de l'intégration d'Unieuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La marge d'EBITDA courant estimée progresse chaque année (5,6 % -&gt; 5,7 % -&gt; 6,5 %), y compris lors de l'exercice d'intégration d'Unieuro (retail électronique en Italie, acquis en novembre 2024). Point à confirmer par segment en data room : cette progression peut recouvrir des dynamiques hétérogènes entre le cœur Fnac Darty et Unieuro, que les communiqués consultés ne permettent pas de distinguer.</t>
   </si>
   <si>
     <t xml:space="preserve">166 M€ d'écart non documenté entre résultat opérationnel et résultat net</t>
@@ -177,7 +268,7 @@
     <t xml:space="preserve">BFR non détaillé publiquement à ce niveau de granularité</t>
   </si>
   <si>
-    <t xml:space="preserve">L'analyse du BFR normalisé (délais clients/fournisseurs/stocks réels, saisonnalité) nécessiterait le détail du bilan et, idéalement, une vue mensuelle - non disponible dans les communiqués annuels consultés.</t>
+    <t xml:space="preserve">L'analyse du BFR normalisé (délais clients/fournisseurs/stocks réels, saisonnalité) nécessiterait le détail du bilan et, idéalement, une vue mensuelle, non disponible dans les communiqués annuels consultés.</t>
   </si>
   <si>
     <t xml:space="preserve">Contrôle</t>
@@ -195,10 +286,13 @@
     <t xml:space="preserve">Marge d'EBITDA courant estimée dans une fourchette plausible (3 %-10 %) sur les 3 exercices</t>
   </si>
   <si>
+    <t xml:space="preserve">EBITDA courant estimé FY2025A recoupe l'EBITDA réel publié (contrôle de cohérence externe)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Synthèse</t>
   </si>
   <si>
-    <t xml:space="preserve">Note : ce contrôle vérifie une identité arithmétique assurée par construction - la ligne C9 de l'onglet 'EBIT to Net Income Bridge' est un plug résiduel calé pour que le pont boucle exactement sur le résultat net publié. Ce n'est pas une validation comptable indépendante du résultat net lui-même.</t>
+    <t xml:space="preserve">Note : ce contrôle vérifie une identité arithmétique assurée par construction : la ligne C9 de l'onglet 'EBIT to Net Income Bridge' est un plug résiduel calé pour que le pont boucle exactement sur le résultat net publié. Ce n'est pas une validation comptable indépendante du résultat net lui-même.</t>
   </si>
 </sst>
 </file>
@@ -212,7 +306,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,11 +391,36 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -324,22 +443,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFB8860B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -408,96 +513,112 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -740,7 +861,7 @@
                   <c:v>0.0569007633587786</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0536515004840271</c:v>
+                  <c:v>0.0645692158760891</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -855,11 +976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="3892480"/>
-        <c:axId val="44134213"/>
+        <c:axId val="62907924"/>
+        <c:axId val="52789311"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="3892480"/>
+        <c:axId val="62907924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -890,7 +1011,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44134213"/>
+        <c:crossAx val="52789311"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -898,7 +1019,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44134213"/>
+        <c:axId val="52789311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -973,7 +1094,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3892480"/>
+        <c:crossAx val="62907924"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1164,11 +1285,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24192913"/>
-        <c:axId val="81554525"/>
+        <c:axId val="56515625"/>
+        <c:axId val="5351454"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24192913"/>
+        <c:axId val="56515625"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1199,7 +1320,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81554525"/>
+        <c:crossAx val="5351454"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1207,7 +1328,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81554525"/>
+        <c:axId val="5351454"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1282,7 +1403,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24192913"/>
+        <c:crossAx val="56515625"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1316,14 +1437,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>116640</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:colOff>112680</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>14040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1331,8 +1452,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="611640" y="3086280"/>
-        <a:ext cx="5755320" cy="2875320"/>
+        <a:off x="611640" y="6724800"/>
+        <a:ext cx="5751360" cy="2871360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1356,9 +1477,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1509120</xdr:colOff>
+      <xdr:colOff>1505160</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>13680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1367,7 +1488,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="611640" y="2933640"/>
-        <a:ext cx="7195320" cy="2875320"/>
+        <a:ext cx="7191360" cy="2871360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1707,7 +1828,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F18"/>
+  <dimension ref="B2:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="54"/>
@@ -1765,69 +1886,68 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <f aca="false">C6*0.034</f>
         <v>267.75</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <f aca="false">D6*0.034</f>
         <v>280.602</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <f aca="false">E6*0.034</f>
-        <v>351.22</v>
+      <c r="E8" s="11" t="n">
+        <v>464</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">C7+C8</f>
         <v>438.75</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <f aca="false">D7+D8</f>
         <v>469.602</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <f aca="false">E7+E8</f>
-        <v>554.22</v>
+        <v>667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <f aca="false">C9/C6</f>
         <v>0.0557142857142857</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <f aca="false">D9/D6</f>
         <v>0.0569007633587786</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <f aca="false">E9/E6</f>
-        <v>0.0536515004840271</v>
+        <v>0.0645692158760891</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <f aca="false">C7/C6</f>
         <v>0.0217142857142857</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <f aca="false">D7/D6</f>
         <v>0.0229007633587786</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <f aca="false">E7/E6</f>
         <v>0.0196515004840271</v>
       </c>
@@ -1869,18 +1989,98 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+    </row>
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+    </row>
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <f aca="false">E9-E29</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="B14:F18"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F27"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1899,7 +2099,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1908,18 +2108,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="B5" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>203</v>
@@ -1927,7 +2127,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>-123</v>
@@ -1935,7 +2135,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>-60</v>
@@ -1943,27 +2143,27 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" s="21" t="n">
         <v>-166</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="C10" s="22" t="n">
         <f aca="false">SUM(C6:C9)</f>
         <v>-146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>-146</v>
@@ -1971,16 +2171,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="23" t="n">
         <f aca="false">C10-C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -2041,108 +2241,108 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="B5" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="B9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="B17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
+      <c r="B21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2183,15 +2383,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21" t="s">
-        <v>51</v>
+      <c r="B6" s="24" t="s">
+        <v>58</v>
       </c>
       <c r="D6" s="10" t="str">
         <f aca="false">IF(ROUND('EBIT to Net Income Bridge'!C13,1)=0,"OK","A VERIFIER")</f>
@@ -2199,8 +2399,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21" t="s">
-        <v>52</v>
+      <c r="B7" s="24" t="s">
+        <v>59</v>
       </c>
       <c r="D7" s="10" t="str">
         <f aca="false">IF(AND('Quality of Earnings'!D7&gt;'Quality of Earnings'!C7,'Quality of Earnings'!E7&gt;'Quality of Earnings'!D7),"OK","A VERIFIER")</f>
@@ -2208,36 +2408,45 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21" t="s">
-        <v>53</v>
+      <c r="B8" s="24" t="s">
+        <v>60</v>
       </c>
       <c r="D8" s="10" t="str">
         <f aca="false">IF(AND(MIN('Quality of Earnings'!C10:E10)&gt;0.03,MAX('Quality of Earnings'!C10:E10)&lt;0.1),"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="10" t="str">
+        <f aca="false">IF(ROUND('Quality of Earnings'!E30,0)=0,"OK","A VERIFIER")</f>
+        <v>OK</v>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C10" s="10" t="str">
-        <f aca="false">IF(COUNTIF(D6:D8,"OK")=3,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
+        <f aca="false">IF(COUNTIF(D6:D9,"OK")=4,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
+      <c r="B12" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B12:E12"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D8">
+  <conditionalFormatting sqref="D6:D9">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>D6="OK"</formula>
     </cfRule>
